--- a/stories/arbres/ATOM-VIV.ANI.001-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Octave marche avec maman. Ils visitent la ferme. Un mouton arrive. Le mouton bêle. Bêê. Maman dit : le mouton bêle. Un chien aboie. Ouaf ouaf. Un chat miaule. Miaou. Une vache meugle. Meuh. Un coq chante. Cocorico. Un canard cancane. Maman dit : chaque animal a un cri. Octave dit le nom de l'animal. Il dit le cri.</t>
+          <t>Octave marche avec maman. Ils visitent la ferme. Un mouton arrive. Le mouton bêle. Bêê. Le mouton bêle. Un chien aboie. Ouaf ouaf. Un chat miaule. Miaou. Une vache meugle. Meuh. Un coq chante. Cocorico. Un canard cancane. Chaque animal a un cri. Octave dit le nom de l'animal. Il dit le cri.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Octave marche avec maman. Ils visitent la ferme. Un mouton arrive. Le mouton bêle. Bêê.
+maman|Le mouton bêle.
+narrateur|Un chien aboie. Ouaf ouaf. Un chat miaule. Miaou. Une vache meugle. Meuh. Un coq chante. Cocorico. Un canard cancane.
+maman|Chaque animal a un cri.
+narrateur|Octave dit le nom de l'animal. Il dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le mouton fait bêê. Quel est son cri ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Octave a nommé l'animal. Il a dit le cri. Mouton, chien, chat, vache, coq, canard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Octave tient la main de maman. La ferme sent le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Octave dit le nom de l'animal. Il dit le cri.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Le mouton fait bêê. Quel est son cri ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,11 @@
           <t>narrateur|Octave a nommé l'animal. Il a dit le cri. Mouton, chien, chat, vache, coq, canard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1855,7 @@
           <t>narrateur|Octave tient la main de maman. La ferme sent le foin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.001-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Octave nomme les cris à la ferme</t>
+          <t>La paille dans la botte</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut le coq de la ferme. Une paille pique dans sa botte. Maman la retire. Puis le coq chante.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Octave marche avec maman. Ils visitent la ferme. Un mouton arrive. Le mouton bêle. Bêê. Le mouton bêle. Un chien aboie. Ouaf ouaf. Un chat miaule. Miaou. Une vache meugle. Meuh. Un coq chante. Cocorico. Un canard cancane. Chaque animal a un cri. Octave dit le nom de l'animal. Il dit le cri.</t>
+          <t>La cour de la ferme sent la paille sèche. Un brin jaune colle au bois. Le soleil tape sur les tuiles. Une ombre passe sur le gravier. Tu sens la paille, Nino ? Oui. Elle pique un peu. On va voir le coq ? Oui. Je veux le coq. En ce moment, Nino marche. Sa botte fait un bruit mou. Un caillou roule sous la semelle. Nino lève le pied. Un brin de paille dépasse. Ça pique. Dans la botte ? Oui. Maman s'accroupit. Elle tire le brin tout doux. La paille sort, toute jaune. Elle est sortie. On remet la botte ? Oui. Nino enfile la botte. Le pied est à l'aise. Ils avancent vers le mur. La cour craque sous les bottes. Une plume grise dort dans la poussière. Un grain de blé brille au soleil. Le coq est où ? On écoute. Le silence pèse un peu. Puis un cri monte du mur. Cocorico. Le coq ! Tu as entendu ? Cocorico. Le coq chante.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Octave marche avec maman. Ils visitent la ferme. Un mouton arrive. Le mouton bêle. Bêê. Maman dit : le mouton bêle. Un chien aboie. Ouaf ouaf. Un chat miaule. Miaou. Une vache meugle. Meuh. Un coq chante. Cocorico. Un canard cancane. Maman dit : chaque animal a un cri. Octave dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; de l'animal. Il dit le cri.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La cour de la ferme sent la paille sèche. Un brin jaune colle au bois. Le soleil tape sur les tuiles. Une ombre passe sur le gravier. Tu sens la paille, Nino ? Oui. Elle pique un peu. On va voir le coq ? Oui. Je veux le coq. En ce moment, Nino marche. Sa botte fait un bruit mou. Un caillou roule sous la semelle. Nino lève le pied. Un brin de paille dépasse. Ça pique. Dans la botte ? Oui. Maman s'accroupit. Elle tire le brin tout doux. La paille sort, toute jaune. Elle est sortie. On remet la botte ? Oui. Nino enfile la botte. Le pied est à l'aise. Ils avancent vers le mur. La cour craque sous les bottes. Une plume grise dort dans la poussière. Un grain de blé brille au soleil. Le coq est où ? On écoute. Le silence pèse un peu. Puis un cri monte du mur. Cocorico. Le coq ! Tu as entendu ? Cocorico. Le coq chante.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Octave marche avec maman. Ils visitent la ferme. Un mouton arrive. Le mouton bêle. Bêê.
-maman|Le mouton bêle.
-narrateur|Un chien aboie. Ouaf ouaf. Un chat miaule. Miaou. Une vache meugle. Meuh. Un coq chante. Cocorico. Un canard cancane.
-maman|Chaque animal a un cri.
-narrateur|Octave dit le nom de l'animal. Il dit le cri.</t>
+          <t>narrateur|La cour de la ferme sent la paille sèche.
+narrateur|Un brin jaune colle au bois.
+narrateur|Le soleil tape sur les tuiles.
+narrateur|Une ombre passe sur le gravier.
+maman|Tu sens la paille, Nino ?
+enfant-m|Oui.
+enfant-m|Elle pique un peu.
+maman|On va voir le coq ?
+enfant-m|Oui.
+enfant-m|Je veux le coq.
+narrateur|En ce moment, Nino marche.
+narrateur|Sa botte fait un bruit mou.
+narrateur|Un caillou roule sous la semelle.
+narrateur|Nino lève le pied.
+narrateur|Un brin de paille dépasse.
+enfant-m|Ça pique.
+maman|Dans la botte ?
+enfant-m|Oui.
+narrateur|Maman s'accroupit.
+narrateur|Elle tire le brin tout doux.
+narrateur|La paille sort, toute jaune.
+enfant-m|Elle est sortie.
+maman|On remet la botte ?
+enfant-m|Oui.
+narrateur|Nino enfile la botte.
+narrateur|Le pied est à l'aise.
+narrateur|Ils avancent vers le mur.
+narrateur|La cour craque sous les bottes.
+narrateur|Une plume grise dort dans la poussière.
+narrateur|Un grain de blé brille au soleil.
+enfant-m|Le coq est où ?
+maman|On écoute.
+narrateur|Le silence pèse un peu.
+narrateur|Puis un cri monte du mur.
+narrateur|Cocorico.
+enfant-m|Le coq !
+maman|Tu as entendu ?
+enfant-m|Cocorico.
+maman|Le coq chante.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1394,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le mouton fait bêê. Quel est son cri ?</t>
+          <t>Nino entend cocorico. Quel est le cri du coq ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le mouton fait bêê. Quel est son &lt;emphasis level="moderate"&gt;cri&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino entend cocorico. Quel est le cri du coq ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1409,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>bêle</t>
+          <t>cocorico</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>bêle | il bêle | bêê | le cri</t>
+          <t>cocorico | il chante | le cri | le coq | chante</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1429,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le mouton bêle. Quel est le cri ?</t>
+          <t>Le coq chante. Quel est le cri ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1478,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1554,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le mouton fait bêê. Quel est son cri ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino entend cocorico.
+narrateur|Quel est le cri du coq ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1582,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Octave a nommé l'animal. Il a dit le cri. Mouton, chien, chat, vache, coq, canard.</t>
+          <t>Le coq est sur le mur chaud. Sa crête est rouge et molle. Je le vois. Merci d'avoir attendu, Nino. Tu as trouvé son cri. Il chante. Oui. Cocorico. Le coq secoue ses plumes. Une poussière d'or tombe. Nino reste près de maman. On le regarde d'ici ? Oui. La botte ne pique plus. Le gravier craque sous le talon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Octave a &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;mé l'animal. Il a dit le cri. Mouton, chien, chat, vache, coq, canard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le coq est sur le mur chaud. Sa crête est rouge et molle. Je le vois. Merci d'avoir attendu, Nino. Tu as trouvé son cri. Il chante. Oui. Cocorico. Le coq secoue ses plumes. Une poussière d'or tombe. Nino reste près de maman. On le regarde d'ici ? Oui. La botte ne pique plus. Le gravier craque sous le talon.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1597,14 +1643,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,7 +1726,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Octave a nommé l'animal. Il a dit le cri. Mouton, chien, chat, vache, coq, canard.</t>
+          <t>narrateur|Le coq est sur le mur chaud.
+narrateur|Sa crête est rouge et molle.
+enfant-m|Je le vois.
+maman|Merci d'avoir attendu, Nino.
+maman|Tu as trouvé son cri.
+enfant-m|Il chante.
+maman|Oui.
+maman|Cocorico.
+narrateur|Le coq secoue ses plumes.
+narrateur|Une poussière d'or tombe.
+narrateur|Nino reste près de maman.
+maman|On le regarde d'ici ?
+enfant-m|Oui.
+narrateur|La botte ne pique plus.
+narrateur|Le gravier craque sous le talon.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1712,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Octave tient la main de maman. La ferme sent le foin.</t>
+          <t>Le coq marche sur le mur. Ses ongles râpent la pierre. Il est grand. Tu voulais le coq. Le voilà. Nino pose le brin de paille. Le brin reste sur le bois. Le coq chante encore une fois. Cocorico. C'est son cri. Une poule gratte loin, tout doux. Nino ne la suit pas. Il écoute le coq. La botte est douce maintenant. Plus de paille. Le pied va bien ? Oui. Un grain roule près du mur. Le coq le regarde, puis chante. Nino pose la main sur le mur chaud. La pierre gratte un peu. Il est beau. Tu as bien écouté. Le brin jaune ne pique plus. Nino regarde encore le mur. Le coq ouvre le bec. Encore. Il chante pour la cour. La poussière d'or retombe.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Octave tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. La ferme sent le foin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le coq marche sur le mur. Ses ongles râpent la pierre. Il est grand. Tu voulais le coq. Le voilà. Nino pose le brin de paille. Le brin reste sur le bois. Le coq chante encore une fois. Cocorico. C'est son cri. Une poule gratte loin, tout doux. Nino ne la suit pas. Il écoute le coq. La botte est douce maintenant. Plus de paille. Le pied va bien ? Oui. Un grain roule près du mur. Le coq le regarde, puis chante. Nino pose la main sur le mur chaud. La pierre gratte un peu. Il est beau. Tu as bien écouté. Le brin jaune ne pique plus. Nino regarde encore le mur. Le coq ouvre le bec. Encore. Il chante pour la cour. La poussière d'or retombe.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1773,14 +1833,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1852,10 +1912,37 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Octave tient la main de maman. La ferme sent le foin.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le coq marche sur le mur.
+narrateur|Ses ongles râpent la pierre.
+enfant-m|Il est grand.
+maman|Tu voulais le coq.
+maman|Le voilà.
+narrateur|Nino pose le brin de paille.
+narrateur|Le brin reste sur le bois.
+narrateur|Le coq chante encore une fois.
+enfant-m|Cocorico.
+maman|C'est son cri.
+narrateur|Une poule gratte loin, tout doux.
+narrateur|Nino ne la suit pas.
+narrateur|Il écoute le coq.
+narrateur|La botte est douce maintenant.
+enfant-m|Plus de paille.
+maman|Le pied va bien ?
+enfant-m|Oui.
+narrateur|Un grain roule près du mur.
+narrateur|Le coq le regarde, puis chante.
+narrateur|Nino pose la main sur le mur chaud.
+narrateur|La pierre gratte un peu.
+enfant-m|Il est beau.
+maman|Tu as bien écouté.
+narrateur|Le brin jaune ne pique plus.
+narrateur|Nino regarde encore le mur.
+narrateur|Le coq ouvre le bec.
+enfant-m|Encore.
+maman|Il chante pour la cour.
+narrateur|La poussière d'or retombe.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1880,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le cocorico reste dans la cour chaude. Nino tient la main de maman. Le coq a chanté. Oui. La paille jaune brille sur le bois.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cocorico reste dans la cour chaude. Nino tient la main de maman. Le coq a chanté. Oui. La paille jaune brille sur le bois.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1941,14 +2028,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2020,10 +2107,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le cocorico reste dans la cour chaude.
+narrateur|Nino tient la main de maman.
+enfant-m|Le coq a chanté.
+maman|Oui.
+narrateur|La paille jaune brille sur le bois.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2042,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>cour de ferme, paille sèche</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Octave, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
